--- a/Outputs/Scenarios/PtX_demand_HR_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HR_Electrification.xlsx
@@ -501,7 +501,7 @@
         <v>0.0008421026685774733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007836259586892495</v>
+        <v>0.0007836259586892498</v>
       </c>
       <c r="F2" t="n">
         <v>0.003293061883258308</v>
@@ -686,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002821052278641758</v>
+        <v>0.0002821052278641759</v>
       </c>
       <c r="F7" t="n">
         <v>4.329939095298978e-05</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009016695477754879</v>
+        <v>0.009016695477754882</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0006539468626333445</v>
+        <v>0.0006539468626333447</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0007197498252196998</v>
+        <v>0.0007197498252196999</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0001223751374429999</v>
+        <v>0.000122375137443</v>
       </c>
       <c r="D31" t="n">
         <v>0.001013892992663411</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0007120277608106362</v>
+        <v>0.0007120277608106361</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.002848111043242545</v>
+        <v>0.002848111043242544</v>
       </c>
     </row>
     <row r="33">
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>6.118756872149997e-05</v>
+        <v>6.118756872149998e-05</v>
       </c>
       <c r="D42" t="n">
         <v>0.0008111143941307289</v>
@@ -1999,7 +1999,7 @@
         <v>5.164820374497096e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0007120277608106362</v>
+        <v>0.0007120277608106361</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_HR_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HR_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0006628818471006026</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007281342268904886</v>
+        <v>0.0008147123759139894</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001213557044817481</v>
+        <v>0.0001568124957807028</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0004854228179269924</v>
+        <v>0.0006272499831228111</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0007281342268904886</v>
+        <v>0.0006272499831228111</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>5.312347484800539e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0010242888742186</v>
+        <v>0.001005603230777765</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0003215565050171282</v>
       </c>
       <c r="K25" t="n">
-        <v>0.009853281813761935</v>
+        <v>0.00967353280415322</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>9.55100534594075e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0001213557044817481</v>
+        <v>0.0001568124957807028</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.000981315871154448</v>
       </c>
       <c r="K30" t="n">
-        <v>0.004272166564863816</v>
+        <v>0.004382070386976757</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0007120277608106361</v>
+        <v>0.0008434429307614697</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.002848111043242544</v>
+        <v>0.003373771723045879</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.004272166564863816</v>
+        <v>0.003373771723045879</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>5.164820374497096e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0007120277608106361</v>
+        <v>0.0008434429307614697</v>
       </c>
     </row>
     <row r="43">
